--- a/reports/report_2026-09-18.xlsx
+++ b/reports/report_2026-09-18.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dbt charts</t>
+          <t>meditation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>3.018</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -475,7 +475,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+charts</t>
+          <t>https://trends.google.com/trends/explore?q=meditation</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dbt v2</t>
+          <t>dbt charts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.369565217391304</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+v2</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+charts</t>
         </is>
       </c>
     </row>
@@ -513,25 +513,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>dbt v2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.369565217391304</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+v2</t>
         </is>
       </c>
     </row>
@@ -541,25 +541,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dbt summit</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9130434782608696</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+summit</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -569,25 +569,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>dbt summit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>0.9130434782608696</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+summit</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7191702488464724</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dbt status tracker</t>
+          <t>data privacy regulations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7173913043478262</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+status+tracker</t>
+          <t>https://trends.google.com/trends/explore?q=data+privacy+regulations</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pfms dbt tracker</t>
+          <t>dbt status tracker</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+tracker</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+status+tracker</t>
         </is>
       </c>
     </row>
@@ -681,25 +681,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pfms dbt status tracker</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.5869565217391305</v>
+        <v>0.7191560682243913</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+status+tracker</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>pfms dbt tracker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5787878787878787</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=pfms+dbt+tracker</t>
         </is>
       </c>
     </row>
@@ -798,26 +798,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("LightDash Demo: Ultimate Setup Guide for Modern BI Tool on DBT | Charts &amp; Metrics Explained", 4.7k views). Your angle: claim the space — straightforward, solid coverage of "dbt charts" has almost no competition right now.</t>
+          <t>REVISIT — "Flying: Relaxing Sleep Music for Meditation, Stress Relief &amp; Relaxation by Peder B. Helland" has 532.1M views, but it's from 10 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>dbt charts</t>
+          <t>meditation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LightDash Demo: Ultimate Setup Guide for Modern BI Tool on DBT | Charts &amp; Metrics Explained</t>
+          <t>Flying: Relaxing Sleep Music for Meditation, Stress Relief &amp; Relaxation by Peder B. Helland</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4709</v>
+        <v>532067862</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>3.018</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+charts</t>
+          <t>https://trends.google.com/trends/explore?q=meditation</t>
         </is>
       </c>
     </row>
@@ -839,26 +839,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PROVEN DEMAND</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PROVEN DEMAND — "Tema El Saxofon 2.0 DBT DjFranyerCarAudio" has 278.1k views from 11 months ago. There's a proven audience for this. Your angle: don't repeat it — bring something only you have (a real client story, a contrarian take, your own data) instead of another generic walkthrough.</t>
+          <t>WHITESPACE — only one relevant video exists ("LightDash Demo: Ultimate Setup Guide for Modern BI Tool on DBT | Charts &amp; Metrics Explained", 4.7k views). Your angle: claim the space — straightforward, solid coverage of "dbt charts" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dbt v2</t>
+          <t>dbt charts</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tema El Saxofon 2.0 DBT DjFranyerCarAudio</t>
+          <t>LightDash Demo: Ultimate Setup Guide for Modern BI Tool on DBT | Charts &amp; Metrics Explained</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>278134</v>
+        <v>4709</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.369565217391304</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+v2</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+charts</t>
         </is>
       </c>
     </row>
@@ -880,38 +880,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OPPORTUNITY</t>
+          <t>PROVEN DEMAND</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Show HN: Capsule – Single-file web apps that save their data into SQLite #Shorts" at 727 views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
+          <t>PROVEN DEMAND — "Tema El Saxofon 2.0 DBT DjFranyerCarAudio" has 278.1k views from 11 months ago. There's a proven audience for this. Your angle: don't repeat it — bring something only you have (a real client story, a contrarian take, your own data) instead of another generic walkthrough.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>dbt v2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite #Shorts</t>
+          <t>Tema El Saxofon 2.0 DBT DjFranyerCarAudio</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>727</v>
+        <v>278139</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>1.369565217391304</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+v2</t>
         </is>
       </c>
     </row>
@@ -921,38 +921,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>OPPORTUNITY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REVISIT — "dbt Explained ft. Anders Swanson" has 34.2k views, but it's from 23 months ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>OPPORTUNITY — a few videos exist but none has broken through (best is "Show HN: Capsule – Single-file web apps that save their data into SQLite #Shorts" at 730 views). Your angle: the existing coverage isn't landing — try a sharper hook, a real example, or a format nobody else has used on this topic.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dbt summit</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>dbt Explained ft. Anders Swanson</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite #Shorts</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>34210</v>
+        <v>730</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9130434782608696</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+summit</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -962,32 +962,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>REVISIT — "dbt Explained ft. Anders Swanson" has 34.2k views, but it's from 23 months ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>dbt summit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>dbt Explained ft. Anders Swanson</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>34209</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>0.9130434782608696</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+summit</t>
         </is>
       </c>
     </row>
@@ -997,38 +1003,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — no real YouTube coverage of "coreyhaines31/marketingskills" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Engineering Course for Beginners</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1131737</v>
-      </c>
+          <t>coreyhaines31/marketingskills</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.7191702488464724</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1043,27 +1043,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WHITESPACE — no real YouTube coverage of "dbt status tracker" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
+          <t>WHITESPACE — only one relevant video exists ("WILL INDIAN GOVERNMENT DESTROY YOUR PRIVACY?? #informative #indiangovernment", 1.6M views). Your angle: claim the space — straightforward, solid coverage of "data privacy regulations" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dbt status tracker</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>data privacy regulations</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WILL INDIAN GOVERNMENT DESTROY YOUR PRIVACY?? #informative #indiangovernment</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1647595</v>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.7173913043478262</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+status+tracker</t>
+          <t>https://trends.google.com/trends/explore?q=data+privacy+regulations</t>
         </is>
       </c>
     </row>
@@ -1078,33 +1084,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("pfms how to check pfms status pfms account balance kaise check kare aapne Android mobile se", 1.6M views). Your angle: claim the space — straightforward, solid coverage of "pfms dbt tracker" has almost no competition right now.</t>
+          <t>WHITESPACE — no real YouTube coverage of "dbt status tracker" yet. Your angle: be first — a clear explainer or tutorial claims this space before anyone else covers it.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pfms dbt tracker</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>pfms how to check pfms status pfms account balance kaise check kare aapne Android mobile se</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1634759</v>
-      </c>
+          <t>dbt status tracker</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+tracker</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+status+tracker</t>
         </is>
       </c>
     </row>
@@ -1114,38 +1114,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WHITESPACE</t>
+          <t>REVISIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WHITESPACE — only one relevant video exists ("pfms how to check pfms status pfms account balance kaise check kare aapne Android mobile se", 1.6M views). Your angle: claim the space — straightforward, solid coverage of "pfms dbt status tracker" has almost no competition right now.</t>
+          <t>REVISIT — "Data Engineering Course for Beginners" has 1.1M views, but it's from 2 years ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>pfms dbt status tracker</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>pfms how to check pfms status pfms account balance kaise check kare aapne Android mobile se</t>
+          <t>Data Engineering Course for Beginners</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1634759</v>
+        <v>1131757</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.5869565217391305</v>
+        <v>0.7191560682243913</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+status+tracker</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>REVISIT</t>
+          <t>WHITESPACE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVISIT — "Data Engineer vs. Data Scientist ft. @eczachly_" has 2.1M views, but it's from 22 months ago — likely stale or off people's radar by now. Your angle: cover what's changed since then, or redo it for today's tools and best practices.</t>
+          <t>WHITESPACE — only one relevant video exists ("pfms how to check pfms status pfms account balance kaise check kare aapne Android mobile se", 1.6M views). Your angle: claim the space — straightforward, solid coverage of "pfms dbt tracker" has almost no competition right now.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>pfms dbt tracker</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Engineer vs. Data Scientist ft. @eczachly_</t>
+          <t>pfms how to check pfms status pfms account balance kaise check kare aapne Android mobile se</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2145656</v>
+        <v>1634766</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.5787878787878787</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=pfms+dbt+tracker</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F164"/>
+  <dimension ref="A1:F171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dbt charts</t>
+          <t>meditation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>3.018</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+charts</t>
+          <t>https://trends.google.com/trends/explore?q=meditation</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dbt v2</t>
+          <t>dbt charts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.369565217391304</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+v2</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+charts</t>
         </is>
       </c>
     </row>
@@ -1298,25 +1298,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
+          <t>dbt v2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.369565217391304</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://withcapsule.app/</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+v2</t>
         </is>
       </c>
     </row>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dbt summit</t>
+          <t>Show HN: Capsule – Single-file web apps that save their data into SQLite</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9130434782608696</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+summit</t>
+          <t>https://withcapsule.app/</t>
         </is>
       </c>
     </row>
@@ -1354,25 +1354,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>dbt summit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>0.9130434782608696</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+summit</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7191702488464724</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dbt status tracker</t>
+          <t>data privacy regulations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7173913043478262</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+status+tracker</t>
+          <t>https://trends.google.com/trends/explore?q=data+privacy+regulations</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pfms dbt tracker</t>
+          <t>dbt status tracker</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+tracker</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+status+tracker</t>
         </is>
       </c>
     </row>
@@ -1466,25 +1466,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pfms dbt status tracker</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.5869565217391305</v>
+        <v>0.7191560682243913</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+status+tracker</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>pfms dbt tracker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5787878787878787</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=pfms+dbt+tracker</t>
         </is>
       </c>
     </row>
@@ -1522,25 +1522,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.5477461844855464</v>
+        <v>0.597</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pfms dbt</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.5444005270092227</v>
+        <v>0.5477353840086759</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pfms dbt status</t>
+          <t>pfms dbt</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.5435217391304348</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=pfms+dbt+status</t>
+          <t>https://trends.google.com/trends/explore?q=pfms+dbt</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dbt boursorama</t>
+          <t>pfms dbt status tracker</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+boursorama</t>
+          <t>https://trends.google.com/trends/explore?q=pfms+dbt+status+tracker</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dbt bourse</t>
+          <t>dbt boursorama</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.4565217391304348</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+bourse</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+boursorama</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>dbt bourse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.3545454545454546</v>
+        <v>0.4565217391304348</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+bourse</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>pfms dbt status</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1699,16 +1699,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.3481168907993848</v>
+        <v>0.4565217391304348</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://trends.google.com/trends/explore?q=pfms+dbt+status</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.3232</v>
+        <v>0.357</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.18842</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1755,16 +1755,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.3</v>
+        <v>0.3481100266193434</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>microsoft power bi</t>
+          <t>Infinite-Parameter LLMs: Generating and Adapting Weights from Live Data</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1783,16 +1783,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.3</v>
+        <v>0.3296</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
+          <t>https://arxiv.org/abs/2609.18842</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>data and analytics</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+and+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -1830,25 +1830,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>data and analytics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.2778877627479592</v>
+        <v>0.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://trends.google.com/trends/explore?q=data+and+analytics</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dbt center of orange county</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+center+of+orange+county</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -1886,16 +1886,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.2303030303030303</v>
+        <v>0.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1923,16 +1923,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.2212121212121212</v>
+        <v>0.2778822833481219</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1951,16 +1951,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.2183065820089127</v>
+        <v>0.234</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -1970,16 +1970,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.2151515151515151</v>
+        <v>0.231</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>what is dbt</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2007,16 +2007,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.2</v>
+        <v>0.2183022774327122</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -2026,16 +2026,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>dbt vs airflow</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.1956521739130435</v>
+        <v>0.213</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+vs+airflow</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -2054,16 +2054,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.201</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>data pipeline solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.1757575757575758</v>
+        <v>0.1986521739130435</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
         </is>
       </c>
     </row>
@@ -2110,16 +2110,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>dbt status</t>
+          <t>dbt vs airflow</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1696969696969697</v>
+        <v>0.1956521739130435</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+status</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+vs+airflow</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>download power bi</t>
+          <t>dbt center of orange county</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.1575757575757576</v>
+        <v>0.1956521739130435</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+center+of+orange+county</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dbt check</t>
+          <t>what is dbt</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.1515151515151515</v>
+        <v>0.195</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+check</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
         </is>
       </c>
     </row>
@@ -2194,16 +2194,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.1454545454545454</v>
+        <v>0.195</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=jobs</t>
         </is>
       </c>
     </row>
@@ -2222,16 +2222,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.1424242424242424</v>
+        <v>0.189</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -2250,16 +2250,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dbt skills</t>
+          <t>dbt status</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.1393939393939394</v>
+        <v>0.171</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+skills</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+status</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>dbt check</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.159</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+check</t>
         </is>
       </c>
     </row>
@@ -2306,16 +2306,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dbt data</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EVERGREEN</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.159</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -2334,16 +2334,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>circular dependency detected power bi</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.156</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>data pipeline solutions</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.144</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -2390,25 +2390,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>dbt skills</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.1247466182908073</v>
+        <v>0.141</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+skills</t>
         </is>
       </c>
     </row>
@@ -2418,16 +2418,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>dbt data</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.1181818181818182</v>
+        <v>0.135</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>power bi free</t>
+          <t>power bi gateway download</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.1151515151515151</v>
+        <v>0.1304347826086956</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+free</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway+download</t>
         </is>
       </c>
     </row>
@@ -2474,16 +2474,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>circular dependency detected power bi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.1151515151515151</v>
+        <v>0.1304347826086956</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://trends.google.com/trends/explore?q=circular+dependency+detected+power+bi</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.1093189257404267</v>
+        <v>0.1247441585329784</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -2530,25 +2530,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.1088</v>
+        <v>0.12</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49736660</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2567,16 +2567,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.108198919430532</v>
+        <v>0.12</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>power bi free</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.1060606060606061</v>
+        <v>0.117</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+free</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.103030303030303</v>
+        <v>0.114</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>dbt pdf</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2651,16 +2651,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.103030303030303</v>
+        <v>0.1093167701863354</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+pdf</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>engineering data management</t>
+          <t>Open-sourced jev architecture last year with model,paper and dataset</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2679,16 +2679,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.1088</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
+          <t>https://news.ycombinator.com/item?id=49736660</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2707,16 +2707,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.1081967859607611</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.108</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2763,16 +2763,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.09660448791260796</v>
+        <v>0.108</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ai data analytics</t>
+          <t>dbt pdf</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.09393939393939395</v>
+        <v>0.108</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=ai+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+pdf</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>business data analytics</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.09393939393939395</v>
+        <v>0.108</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=business+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>engineering data management</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.08787878787878788</v>
+        <v>0.102</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>social engineering</t>
+          <t>data engineering and analytics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0818181818181818</v>
+        <v>0.099</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+and+analytics</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>powerbi</t>
+          <t>ai data analytics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.0818181818181818</v>
+        <v>0.099</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=powerbi</t>
+          <t>https://trends.google.com/trends/explore?q=ai+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2931,16 +2931,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.0818181818181818</v>
+        <v>0.0966025830622104</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>data engineer</t>
+          <t>business data analytics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.0818181818181818</v>
+        <v>0.093</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=business+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>powerbi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.0818181818181818</v>
+        <v>0.09</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=powerbi</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.07575757575757576</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>power bi gateway</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.07575757575757576</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
+          <t>https://trends.google.com/trends/explore?q=travel</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3071,16 +3071,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.07565563749654929</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.07272727272727272</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.07272727272727272</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.06969696969696969</v>
+        <v>0.081</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.06969696969696969</v>
+        <v>0.081</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -3202,16 +3202,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>social engineering</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.081</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>power bi gateway download</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.06521739130434782</v>
+        <v>0.081</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+gateway+download</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>power bi app</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3267,16 +3267,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.06363636363636363</v>
+        <v>0.07565414571625752</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+app</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -3286,16 +3286,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>dbt meaning</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.06363636363636363</v>
+        <v>0.075</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+meaning</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3323,16 +3323,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.06120597862523169</v>
+        <v>0.075</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>snowflake</t>
+          <t>data science pipeline</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.07421739130434782</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake</t>
+          <t>https://trends.google.com/trends/explore?q=data+science+pipeline</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>snowflake dbt</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.0606060606060606</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+dbt</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>business analytics</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.05454545454545454</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=business+analytics</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.05454545454545454</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.05454545454545454</v>
+        <v>0.066</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3482,25 +3482,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.05330283550893244</v>
+        <v>0.066</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+jobs</t>
         </is>
       </c>
     </row>
@@ -3510,25 +3510,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>dbt meaning</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.05167803762274718</v>
+        <v>0.063</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+meaning</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>dbt analytics engineering certification</t>
+          <t>snowflake dbt</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.05151515151515151</v>
+        <v>0.063</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+dbt</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>dbt training</t>
+          <t>snowflake</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.04848484848484848</v>
+        <v>0.063</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+training</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3603,16 +3603,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.04848484848484848</v>
+        <v>0.06120477176377798</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop+download</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.04848484848484848</v>
+        <v>0.057</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>power bi reports</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.04848484848484848</v>
+        <v>0.057</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+reports</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>power bi reports</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3687,16 +3687,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.04839689237685846</v>
+        <v>0.057</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+reports</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>data analytics services</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.057</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+services</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3743,16 +3743,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.04242424242424242</v>
+        <v>0.05330178448190871</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.04076191978546358</v>
+        <v>0.05167701863354038</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>data analytics services</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3799,16 +3799,16 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.03803289032614268</v>
+        <v>0.051</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+services</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.03778049453799739</v>
+        <v>0.04839593808537909</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.048</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://trends.google.com/trends/explore?q=music</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3883,16 +3883,16 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.02923058721457586</v>
+        <v>0.048</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3911,16 +3911,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.02818945458847655</v>
+        <v>0.045</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>data analytics healthcare</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.02727272727272727</v>
+        <v>0.04076111604061915</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+healthcare</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.02697479985802737</v>
+        <v>0.03803214039238884</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.02615451354655519</v>
+        <v>0.03777974958099182</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4023,16 +4023,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.02490830934258785</v>
+        <v>0.036</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -4042,25 +4042,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.02424242424242424</v>
+        <v>0.02923001084491768</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4079,16 +4079,16 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.02424242424242424</v>
+        <v>0.02818889874790496</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>data scientist</t>
+          <t>data analytics healthcare</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.02121212121212121</v>
+        <v>0.027</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+scientist</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+healthcare</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>data analytics tools</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.02121212121212121</v>
+        <v>0.027</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4163,16 +4163,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.02110659778364949</v>
+        <v>0.027</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.01970264621209133</v>
+        <v>0.02697426796805679</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.02615399783101646</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -4238,25 +4238,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.02490781819974366</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -4266,16 +4266,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>data analytics masters</t>
+          <t>data analytics tools</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.01212121212121212</v>
+        <v>0.024</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+masters</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4303,16 +4303,16 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.01212121212121212</v>
+        <v>0.02110618160307601</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.01140513467681508</v>
+        <v>0.01970225771468008</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -4350,25 +4350,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.009953858894979691</v>
+        <v>0.018</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4387,16 +4387,16 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.009401743108411879</v>
+        <v>0.018</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4406,16 +4406,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.00909090909090909</v>
+        <v>0.015</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>data analytics masters</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.007256378909176953</v>
+        <v>0.015</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+masters</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
+          <t>google data analytics certificate</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4471,16 +4471,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.006399999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://github.com/poundifdef/plainoldanalytics</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certificate</t>
         </is>
       </c>
     </row>
@@ -4490,25 +4490,25 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.006399999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://sentralis.io/</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -4518,16 +4518,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>EVERGREEN</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.006060606060606061</v>
+        <v>0.012</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>google data analytics certificate</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4555,16 +4555,16 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.006060606060606061</v>
+        <v>0.01140490979000296</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certificate</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>what is big data analytics</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4583,16 +4583,16 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.006060606060606061</v>
+        <v>0.009953662624470078</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+big+data+analytics</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>masters in data analytics</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4611,16 +4611,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.006060606060606061</v>
+        <v>0.009401557724539092</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=masters+in+data+analytics</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>masters in data analytics</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4639,16 +4639,16 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.005394959971605474</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=masters+in+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>We Benchmark Analytics Agents, this explains how</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.0032</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>what is big data analytics</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4695,16 +4695,16 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.003186496825334227</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>aws data pipeline</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4723,16 +4723,16 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.007256235827664399</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=aws+data+pipeline</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -4742,25 +4742,25 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>Show HN: Crypto portfolio risk and scenario analysis with AI agents on top</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.006399999999999999</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://sentralis.io/</t>
         </is>
       </c>
     </row>
@@ -4770,25 +4770,25 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>Show HN: Plainoldanalytics: Analytics Middlware for Go</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.006399999999999999</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://github.com/poundifdef/plainoldanalytics</t>
         </is>
       </c>
     </row>
@@ -4798,16 +4798,16 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>data pipeline software</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.006</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>data pipeline software</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.00303030303030303</v>
+        <v>0.006</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4863,16 +4863,16 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.002744804196079978</v>
+        <v>0.006</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>data pipeline aws</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4891,16 +4891,16 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.002034941041921363</v>
+        <v>0.006</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
         </is>
       </c>
     </row>
@@ -4910,25 +4910,25 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.001956067358125961</v>
+        <v>0.006</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.001719446306739756</v>
+        <v>0.005394853593611358</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MUJTBA4F/attrition-insights-engineering</t>
+          <t>We Benchmark Analytics Agents, this explains how</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4975,16 +4975,16 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.001609023149426194</v>
+        <v>0.0032</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://github.com/MUJTBA4F/attrition-insights-engineering</t>
+          <t>https://benchouse.ai/blog/how-we-benchmark-analytics-agents</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.001530149465630792</v>
+        <v>0.003186433993887411</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5031,16 +5031,16 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.001482825255353551</v>
+        <v>0.003</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5059,16 +5059,16 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.001277753677485507</v>
+        <v>0.003</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>dbt analytics engineering certification</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5087,16 +5087,16 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.001277753677485507</v>
+        <v>0.003</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+analytics+engineering+certification</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>etl data pipeline</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5115,16 +5115,16 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.001261978940726427</v>
+        <v>0.003</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5134,25 +5134,25 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NEW / SPIKE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.001198879993690105</v>
+        <v>0.003</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.001198879993690105</v>
+        <v>0.00274475007394262</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.001167330520171945</v>
+        <v>0.002034900916888494</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.001009583152581141</v>
+        <v>0.001956028788326925</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.0007887368379540168</v>
+        <v>0.001719412402642216</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>MUJTBA4F/attrition-insights-engineering</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.0005994399968450527</v>
+        <v>0.001608991422656019</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://github.com/MUJTBA4F/attrition-insights-engineering</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.0004890168395314903</v>
+        <v>0.001530119294094449</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.00047324210277241</v>
+        <v>0.001482796016957508</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.0003943684189770084</v>
+        <v>0.001277728482697427</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.0003470442086997673</v>
+        <v>0.001277728482697427</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.000283945261663446</v>
+        <v>0.001261954056985113</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.000189296841108964</v>
+        <v>0.001198856354135857</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.000141972630831723</v>
+        <v>0.001198856354135857</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.0001261978940726427</v>
+        <v>0.001167307502711229</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3.154947351816067e-05</v>
+        <v>0.00100956324558809</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>errajeshcs-pixel/DS4Earth</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5563,7 +5563,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1.577473675908033e-05</v>
+        <v>0.0007887212856156956</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Amey-Thakur/OPTIMIZING-STOCK-TRADING-STRATEGY-WITH-K-MEANS-CLUSTERING</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>0.0005994281770679287</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://github.com/Amey-Thakur/OPTIMIZING-STOCK-TRADING-STRATEGY-WITH-K-MEANS-CLUSTERING</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5619,16 +5619,16 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>0.0004890071970817312</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5647,16 +5647,16 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>0.0004732327713694173</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -5666,25 +5666,25 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>NEW / SPIKE</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>0.0003943606428078478</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>etl data pipeline</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5703,16 +5703,16 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>0.0003470373656709061</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5731,16 +5731,16 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>0.0002839396628216504</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://etlfunnel.com</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5759,16 +5759,16 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>0.0001892931085477669</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
     </row>
@@ -5778,23 +5778,219 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
+          <t>exmergo/dex</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0.0001419698314108252</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://github.com/exmergo/dex</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0.0001261954056985113</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>3.154885142462782e-05</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1.577442571231391e-05</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://github.com/errajeshcs-pixel/DS4Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Amey-Thakur/OPTIMIZING-STOCK-TRADING-STRATEGY-WITH-K-MEANS-CLUSTERING</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://github.com/Amey-Thakur/OPTIMIZING-STOCK-TRADING-STRATEGY-WITH-K-MEANS-CLUSTERING</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Show HN: ETLFunnel – self-hosted, code-first data pipelines (v1.1.1)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://etlfunnel.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Spec-Lock-Diff: a framework for agentic dbt development</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://github.com/miloskimatheus/spec-lock-diff/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
           <t>what does dbt stand for</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
         <v>0</v>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>trends</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
         <is>
           <t>https://trends.google.com/trends/explore?q=what+does+dbt+stand+for</t>
         </is>
@@ -5811,7 +6007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A278"/>
+  <dimension ref="A1:A279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6370,7 +6566,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>data analytics apprenticeship</t>
+          <t>data analytics apprenticeship google</t>
         </is>
       </c>
     </row>
@@ -6412,21 +6608,21 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>data analytics meaning</t>
+          <t>data analytics jobs remote</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>data analytics meaning</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>data analytics wsu</t>
+          <t>data analytics salary</t>
         </is>
       </c>
     </row>
@@ -7056,21 +7252,21 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>power bi app</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>power bi certification</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>power bi dashboard examples</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
     </row>
@@ -7217,544 +7413,551 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data engineering</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>what is dbt</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>what is dbt data</t>
+          <t>what is dbt</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>what is dbt in data engineering</t>
+          <t>what is dbt data</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>what is dbt treatment</t>
+          <t>what is dbt in data engineering</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>what is dbt used for</t>
+          <t>what is dbt treatment</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is dbt used for</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is power bi</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>what is power bi dashboard</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>what is power bi dashboard</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>what is power bi service</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>what is power bi software</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why data analytics</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics course</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data engineering</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>why dbt</t>
+          <t>why data pipeline</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>why dbt app is not working</t>
+          <t>why dbt</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>why dbt is used</t>
+          <t>why dbt app is not working</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>why dbt is used in data engineering</t>
+          <t>why dbt is used</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>why dbt is used in data engineering</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>why power bi</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>why power bi is important</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>why power bi is used</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
+        <is>
+          <t>why power bi over tableau</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>workflow vs data pipeline</t>
         </is>
